--- a/praksa/RAST/dnevnik_rada.xlsx
+++ b/praksa/RAST/dnevnik_rada.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RAST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruno\Desktop\dipl\praksa\RAST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F85CB3-963F-4765-8168-604FE6620080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077DFB76-B013-4C9B-A24C-C06BE51F7927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{98FA4047-CAE0-4706-9DDF-D3B87A716F42}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{98FA4047-CAE0-4706-9DDF-D3B87A716F42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>DNEVNIK RADA</t>
   </si>
@@ -65,6 +65,20 @@
     <t xml:space="preserve">upoznavanje sa radnom okolinom i kolegama
  upoznavanje s problemima na stranicama,
  prvi koraci u wordpressu bebuilder temi </t>
+  </si>
+  <si>
+    <t>03.03.2026.</t>
+  </si>
+  <si>
+    <t>odradeno</t>
+  </si>
+  <si>
+    <t>odradeno dana</t>
+  </si>
+  <si>
+    <t>dodatno upoznavanje se bebuilder sučeljem
+ucenje konfiguracije razlicitih sekcija i wrapova s elementima u njima,
+ za vjezubu prema "hardcoded" slikama kreiranje elemenata koji isto izgledaju ali su konfigurabilniji</t>
   </si>
 </sst>
 </file>
@@ -127,20 +141,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -492,53 +508,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFA104E-2CAC-46AB-9E25-6D94391EA416}">
-  <dimension ref="B1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="119.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="119.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2"/>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <f>SUM(Table1[sati])</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="7">
+        <f>SUM(Table1[sati])/240</f>
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="8">
+        <f>COUNTIF(Table1[sati],"&gt;0")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>3</v>
       </c>
@@ -549,15 +580,26 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
